--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R3b5bd4ac46cd4016"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R14bb4108c38a4ab0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R867e9b4075f7431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R8646f87cc8884cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcd8f80aec7894503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R6933d9458941401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R2d7e78e02d0244f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rd4ccd9b1394d433c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R50e17d599b4446d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R715a6b460ee74705"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1525,7 +1525,7 @@
         <x:v>日志与临时文件</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>可增加Playwright运行日志或失败诊断</x:v>
+        <x:v>可增加Playwright运行日志</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
         <x:v>附加文件不能代替规定源码、复核表、回执或截图</x:v>
@@ -1547,10 +1547,10 @@
         <x:v>执行顺序</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>六个case可以按输入顺序或case_id排序串行执行</x:v>
+        <x:v>场景可以按输入顺序或case_id排序串行执行</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>不能共享已登录上下文或漏测任一case</x:v>
+        <x:v>不能共享已登录上下文或漏测输入场景</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
